--- a/Client/Bin/Resources/Data/xlsx/DT_Terrain.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_Terrain.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moon\Desktop\Jusin\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9F15151-8278-4653-8DD0-6DA70DEFC077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B3F4AE-DBB2-401F-8327-813627D57F5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5097B461-088A-4279-A51D-67C0C1E8A878}"/>
   </bookViews>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>Type</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Id</t>
   </si>
@@ -38,9 +35,6 @@
   </si>
   <si>
     <t>Extra</t>
-  </si>
-  <si>
-    <t>Terrain</t>
   </si>
   <si>
     <t>COMPONENT_TYPE_TERRAIN</t>
@@ -1001,10 +995,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{734F45BF-BC4E-47D1-A710-EC0D8EC85C6C}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1020,22 +1014,16 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
